--- a/data/editorial_es.xlsx
+++ b/data/editorial_es.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
   <si>
     <t xml:space="preserve">what</t>
   </si>
@@ -55,35 +55,7 @@
     <t xml:space="preserve">Contribuir al consejo editorial, centrándose en la representación y la diversidad del Sur Global</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">\href{https://evohuman.org/edhb/editorial-board}{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">Comité editorial</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
-    </r>
+    <t xml:space="preserve">\href{https://evohuman.org/edhb/editorial-board}{Comité editorial}</t>
   </si>
   <si>
     <t xml:space="preserve">Data Editor</t>
@@ -202,6 +174,9 @@
   </si>
   <si>
     <t xml:space="preserve">\href{https://www.sciencedirect.com/journal/cortex}{Cortex}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\href{https://link.springer.com/journal/12110}{Human Nature}</t>
   </si>
   <si>
     <t xml:space="preserve">\href{https://www.springer.com/journal/10919/}{Journal of Nonverbal Behavior}</t>
@@ -286,6 +261,7 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -343,7 +319,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -366,6 +342,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -392,37 +372,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
@@ -561,7 +541,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultColWidth="11.43359375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.29"/>
@@ -803,81 +783,87 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="E26" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="E27" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="1" t="s">
+      <c r="E28" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="1" t="s">
+      <c r="D29" s="7"/>
+      <c r="E29" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D29" s="6"/>
-      <c r="E29" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="6"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D31" s="6"/>
+      <c r="D31" s="7"/>
       <c r="E31" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D32" s="7"/>
       <c r="E32" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="1" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E34" s="1" t="s">
         <v>63</v>
       </c>
     </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E35" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" display="https://evohuman.org/edhb/editorial-board"/>
+    <hyperlink ref="E4" r:id="rId1" display="\href{https://evohuman.org/edhb/editorial-board}{Comité editorial}"/>
     <hyperlink ref="E19" r:id="rId2" display="\href{https://nyaspubs.onlinelibrary.wiley.com/journal/17496632}{Annals of the New York Academy of Sciences}"/>
+    <hyperlink ref="E25" r:id="rId3" display="https://link.springer.com/journal/12110"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
